--- a/outputs/384-4.xlsx
+++ b/outputs/384-4.xlsx
@@ -115,8 +115,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -313,66 +317,66 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="0" t="n">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0" t="n">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -396,27 +400,27 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -440,22 +444,22 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>5</v>
       </c>
     </row>
